--- a/data/stocks_20260407_111326.xlsx
+++ b/data/stocks_20260407_111326.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,69 +1119,69 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>217.54</v>
+        <v>458.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1.76</v>
+        <v>0.75</v>
       </c>
       <c r="E10" t="n">
-        <v>214.98</v>
+        <v>452.99</v>
       </c>
       <c r="F10" t="n">
-        <v>216.09</v>
+        <v>457.19</v>
       </c>
       <c r="G10" t="n">
-        <v>223.44</v>
+        <v>437.33</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.609</v>
+        <v>15.684</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.922</v>
+        <v>15.83</v>
       </c>
       <c r="J10" t="n">
-        <v>43.44</v>
+        <v>40.33</v>
       </c>
       <c r="K10" t="n">
-        <v>42.09</v>
+        <v>46.5</v>
       </c>
       <c r="L10" t="n">
-        <v>46.15</v>
+        <v>28.01</v>
       </c>
       <c r="M10" t="n">
-        <v>49.32</v>
+        <v>56.7</v>
       </c>
       <c r="N10" t="n">
-        <v>43.89</v>
+        <v>57.34</v>
       </c>
       <c r="O10" t="n">
-        <v>44.33</v>
+        <v>55.92</v>
       </c>
       <c r="P10" t="n">
-        <v>1987.11</v>
+        <v>2841.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1794.84</v>
+        <v>3983.86</v>
       </c>
       <c r="R10" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="S10" t="n">
-        <v>214</v>
+        <v>450</v>
       </c>
       <c r="T10" t="n">
-        <v>223.85</v>
+        <v>468</v>
       </c>
       <c r="U10" t="n">
-        <v>211</v>
+        <v>441.19</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
@@ -1192,69 +1192,69 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>458.7</v>
+        <v>317.36</v>
       </c>
       <c r="D11" t="n">
-        <v>0.75</v>
+        <v>-4.94</v>
       </c>
       <c r="E11" t="n">
-        <v>452.99</v>
+        <v>321.79</v>
       </c>
       <c r="F11" t="n">
-        <v>457.19</v>
+        <v>318.52</v>
       </c>
       <c r="G11" t="n">
-        <v>437.33</v>
+        <v>316.43</v>
       </c>
       <c r="H11" t="n">
-        <v>15.684</v>
+        <v>6.257</v>
       </c>
       <c r="I11" t="n">
-        <v>15.83</v>
+        <v>6.934</v>
       </c>
       <c r="J11" t="n">
-        <v>40.33</v>
+        <v>59.46</v>
       </c>
       <c r="K11" t="n">
-        <v>46.5</v>
+        <v>60.37</v>
       </c>
       <c r="L11" t="n">
-        <v>28.01</v>
+        <v>57.65</v>
       </c>
       <c r="M11" t="n">
-        <v>56.7</v>
+        <v>48.54</v>
       </c>
       <c r="N11" t="n">
-        <v>57.34</v>
+        <v>50.96</v>
       </c>
       <c r="O11" t="n">
-        <v>55.92</v>
+        <v>53.47</v>
       </c>
       <c r="P11" t="n">
-        <v>2841.74</v>
+        <v>3290.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>3983.86</v>
+        <v>3403.01</v>
       </c>
       <c r="R11" t="n">
-        <v>0.71</v>
+        <v>0.97</v>
       </c>
       <c r="S11" t="n">
-        <v>450</v>
+        <v>334.02</v>
       </c>
       <c r="T11" t="n">
-        <v>468</v>
+        <v>336.83</v>
       </c>
       <c r="U11" t="n">
-        <v>441.19</v>
+        <v>314.85</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
@@ -1265,69 +1265,69 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300394</v>
+        <v>988</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>317.36</v>
+        <v>104.2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.94</v>
+        <v>0.64</v>
       </c>
       <c r="E12" t="n">
-        <v>321.79</v>
+        <v>103.26</v>
       </c>
       <c r="F12" t="n">
-        <v>318.52</v>
+        <v>106.59</v>
       </c>
       <c r="G12" t="n">
-        <v>316.43</v>
+        <v>113.17</v>
       </c>
       <c r="H12" t="n">
-        <v>6.257</v>
+        <v>1.194</v>
       </c>
       <c r="I12" t="n">
-        <v>6.934</v>
+        <v>3.706</v>
       </c>
       <c r="J12" t="n">
-        <v>59.46</v>
+        <v>16.86</v>
       </c>
       <c r="K12" t="n">
-        <v>60.37</v>
+        <v>16.09</v>
       </c>
       <c r="L12" t="n">
-        <v>57.65</v>
+        <v>18.39</v>
       </c>
       <c r="M12" t="n">
-        <v>48.54</v>
+        <v>42.8</v>
       </c>
       <c r="N12" t="n">
-        <v>50.96</v>
+        <v>47.47</v>
       </c>
       <c r="O12" t="n">
-        <v>53.47</v>
+        <v>52.43</v>
       </c>
       <c r="P12" t="n">
-        <v>3290.08</v>
+        <v>5710.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>3403.01</v>
+        <v>10602.21</v>
       </c>
       <c r="R12" t="n">
-        <v>0.97</v>
+        <v>0.54</v>
       </c>
       <c r="S12" t="n">
-        <v>334.02</v>
+        <v>104.88</v>
       </c>
       <c r="T12" t="n">
-        <v>336.83</v>
+        <v>108.5</v>
       </c>
       <c r="U12" t="n">
-        <v>314.85</v>
+        <v>103.26</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
@@ -1338,69 +1338,69 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>988</v>
+        <v>603986</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104.2</v>
+        <v>249.66</v>
       </c>
       <c r="D13" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="E13" t="n">
-        <v>103.26</v>
+        <v>247.77</v>
       </c>
       <c r="F13" t="n">
-        <v>106.59</v>
+        <v>256.75</v>
       </c>
       <c r="G13" t="n">
-        <v>113.17</v>
+        <v>273.41</v>
       </c>
       <c r="H13" t="n">
-        <v>1.194</v>
+        <v>-10.599</v>
       </c>
       <c r="I13" t="n">
-        <v>3.706</v>
+        <v>-7.152</v>
       </c>
       <c r="J13" t="n">
-        <v>16.86</v>
+        <v>23.39</v>
       </c>
       <c r="K13" t="n">
-        <v>16.09</v>
+        <v>23.26</v>
       </c>
       <c r="L13" t="n">
-        <v>18.39</v>
+        <v>23.66</v>
       </c>
       <c r="M13" t="n">
-        <v>42.8</v>
+        <v>38.03</v>
       </c>
       <c r="N13" t="n">
-        <v>47.47</v>
+        <v>39.7</v>
       </c>
       <c r="O13" t="n">
-        <v>52.43</v>
+        <v>44.38</v>
       </c>
       <c r="P13" t="n">
-        <v>5710.42</v>
+        <v>1984.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>10602.21</v>
+        <v>2984.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="S13" t="n">
-        <v>104.88</v>
+        <v>253.1</v>
       </c>
       <c r="T13" t="n">
-        <v>108.5</v>
+        <v>255.96</v>
       </c>
       <c r="U13" t="n">
-        <v>103.26</v>
+        <v>248.81</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
@@ -1411,69 +1411,69 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603986</v>
+        <v>300042</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>249.66</v>
+        <v>42.11</v>
       </c>
       <c r="D14" t="n">
-        <v>0.22</v>
+        <v>1.59</v>
       </c>
       <c r="E14" t="n">
-        <v>247.77</v>
+        <v>42.12</v>
       </c>
       <c r="F14" t="n">
-        <v>256.75</v>
+        <v>44.02</v>
       </c>
       <c r="G14" t="n">
-        <v>273.41</v>
+        <v>45.42</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.599</v>
+        <v>1.117</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.152</v>
+        <v>2.334</v>
       </c>
       <c r="J14" t="n">
-        <v>23.39</v>
+        <v>9.27</v>
       </c>
       <c r="K14" t="n">
-        <v>23.26</v>
+        <v>15.1</v>
       </c>
       <c r="L14" t="n">
-        <v>23.66</v>
+        <v>-2.39</v>
       </c>
       <c r="M14" t="n">
-        <v>38.03</v>
+        <v>39.27</v>
       </c>
       <c r="N14" t="n">
-        <v>39.7</v>
+        <v>47.6</v>
       </c>
       <c r="O14" t="n">
-        <v>44.38</v>
+        <v>52.81</v>
       </c>
       <c r="P14" t="n">
-        <v>1984.72</v>
+        <v>1910.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2984.5</v>
+        <v>3070.08</v>
       </c>
       <c r="R14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="S14" t="n">
-        <v>253.1</v>
+        <v>41.92</v>
       </c>
       <c r="T14" t="n">
-        <v>255.96</v>
+        <v>43.54</v>
       </c>
       <c r="U14" t="n">
-        <v>248.81</v>
+        <v>41.18</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
@@ -1484,69 +1484,69 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688525</v>
+        <v>300302</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>217.42</v>
+        <v>19.85</v>
       </c>
       <c r="D15" t="n">
-        <v>3.39</v>
+        <v>6.26</v>
       </c>
       <c r="E15" t="n">
-        <v>213.22</v>
+        <v>19.57</v>
       </c>
       <c r="F15" t="n">
-        <v>226.03</v>
+        <v>20.6</v>
       </c>
       <c r="G15" t="n">
-        <v>226.97</v>
+        <v>21.29</v>
       </c>
       <c r="H15" t="n">
-        <v>7.051</v>
+        <v>-0.129</v>
       </c>
       <c r="I15" t="n">
-        <v>12.133</v>
+        <v>0.285</v>
       </c>
       <c r="J15" t="n">
-        <v>14.74</v>
+        <v>11.86</v>
       </c>
       <c r="K15" t="n">
-        <v>24.59</v>
+        <v>13.41</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.95</v>
+        <v>8.75</v>
       </c>
       <c r="M15" t="n">
-        <v>45.19</v>
+        <v>43.02</v>
       </c>
       <c r="N15" t="n">
-        <v>50.53</v>
+        <v>45.67</v>
       </c>
       <c r="O15" t="n">
-        <v>54.87</v>
+        <v>48.36</v>
       </c>
       <c r="P15" t="n">
-        <v>3005.87</v>
+        <v>4430.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>3879.9</v>
+        <v>4300.15</v>
       </c>
       <c r="R15" t="n">
-        <v>0.77</v>
+        <v>1.03</v>
       </c>
       <c r="S15" t="n">
-        <v>216</v>
+        <v>19.32</v>
       </c>
       <c r="T15" t="n">
-        <v>224.3</v>
+        <v>21.06</v>
       </c>
       <c r="U15" t="n">
-        <v>214.66</v>
+        <v>19.03</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
@@ -1557,69 +1557,69 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300042</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>深华发A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42.11</v>
+        <v>15.23</v>
       </c>
       <c r="D16" t="n">
-        <v>1.59</v>
+        <v>2.77</v>
       </c>
       <c r="E16" t="n">
-        <v>42.12</v>
+        <v>15.53</v>
       </c>
       <c r="F16" t="n">
-        <v>44.02</v>
+        <v>16.46</v>
       </c>
       <c r="G16" t="n">
-        <v>45.42</v>
+        <v>17.07</v>
       </c>
       <c r="H16" t="n">
-        <v>1.117</v>
+        <v>-0.047</v>
       </c>
       <c r="I16" t="n">
-        <v>2.334</v>
+        <v>0.425</v>
       </c>
       <c r="J16" t="n">
-        <v>9.27</v>
+        <v>8.24</v>
       </c>
       <c r="K16" t="n">
-        <v>15.1</v>
+        <v>12.54</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.39</v>
+        <v>-0.35</v>
       </c>
       <c r="M16" t="n">
-        <v>39.27</v>
+        <v>34.52</v>
       </c>
       <c r="N16" t="n">
-        <v>47.6</v>
+        <v>42.44</v>
       </c>
       <c r="O16" t="n">
-        <v>52.81</v>
+        <v>46.75</v>
       </c>
       <c r="P16" t="n">
-        <v>1910.52</v>
+        <v>907.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>3070.08</v>
+        <v>1340.01</v>
       </c>
       <c r="R16" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="S16" t="n">
-        <v>41.92</v>
+        <v>14.82</v>
       </c>
       <c r="T16" t="n">
-        <v>43.54</v>
+        <v>15.26</v>
       </c>
       <c r="U16" t="n">
-        <v>41.18</v>
+        <v>14.82</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
@@ -1630,69 +1630,69 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>300302</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.85</v>
+        <v>35.68</v>
       </c>
       <c r="D17" t="n">
-        <v>6.26</v>
+        <v>-2.65</v>
       </c>
       <c r="E17" t="n">
-        <v>19.57</v>
+        <v>37.18</v>
       </c>
       <c r="F17" t="n">
-        <v>20.6</v>
+        <v>37.35</v>
       </c>
       <c r="G17" t="n">
-        <v>21.29</v>
+        <v>37.33</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.129</v>
+        <v>-0.197</v>
       </c>
       <c r="I17" t="n">
-        <v>0.285</v>
+        <v>-0.049</v>
       </c>
       <c r="J17" t="n">
-        <v>11.86</v>
+        <v>33.91</v>
       </c>
       <c r="K17" t="n">
-        <v>13.41</v>
+        <v>46.63</v>
       </c>
       <c r="L17" t="n">
-        <v>8.75</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>43.02</v>
+        <v>35.22</v>
       </c>
       <c r="N17" t="n">
-        <v>45.67</v>
+        <v>43.19</v>
       </c>
       <c r="O17" t="n">
-        <v>48.36</v>
+        <v>47.46</v>
       </c>
       <c r="P17" t="n">
-        <v>4430.07</v>
+        <v>3990.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>4300.15</v>
+        <v>5992.46</v>
       </c>
       <c r="R17" t="n">
-        <v>1.03</v>
+        <v>0.67</v>
       </c>
       <c r="S17" t="n">
-        <v>19.32</v>
+        <v>36.65</v>
       </c>
       <c r="T17" t="n">
-        <v>21.06</v>
+        <v>37</v>
       </c>
       <c r="U17" t="n">
-        <v>19.03</v>
+        <v>35.6</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
@@ -1703,69 +1703,69 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>300017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深华发A</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.23</v>
+        <v>16.05</v>
       </c>
       <c r="D18" t="n">
-        <v>2.77</v>
+        <v>-3.02</v>
       </c>
       <c r="E18" t="n">
-        <v>15.53</v>
+        <v>16.76</v>
       </c>
       <c r="F18" t="n">
-        <v>16.46</v>
+        <v>17.13</v>
       </c>
       <c r="G18" t="n">
-        <v>17.07</v>
+        <v>17.67</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.047</v>
+        <v>-0.314</v>
       </c>
       <c r="I18" t="n">
-        <v>0.425</v>
+        <v>-0.074</v>
       </c>
       <c r="J18" t="n">
-        <v>8.24</v>
+        <v>15.05</v>
       </c>
       <c r="K18" t="n">
-        <v>12.54</v>
+        <v>23.88</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.35</v>
+        <v>-2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>34.52</v>
+        <v>31.98</v>
       </c>
       <c r="N18" t="n">
-        <v>42.44</v>
+        <v>40.06</v>
       </c>
       <c r="O18" t="n">
-        <v>46.75</v>
+        <v>47.28</v>
       </c>
       <c r="P18" t="n">
-        <v>907.78</v>
+        <v>14241.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>1340.01</v>
+        <v>24656.41</v>
       </c>
       <c r="R18" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="S18" t="n">
-        <v>14.82</v>
+        <v>16.49</v>
       </c>
       <c r="T18" t="n">
-        <v>15.26</v>
+        <v>16.69</v>
       </c>
       <c r="U18" t="n">
-        <v>14.82</v>
+        <v>15.95</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
@@ -1776,69 +1776,69 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>603881</v>
+        <v>300418</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>35.68</v>
+        <v>47.22</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.65</v>
+        <v>1.72</v>
       </c>
       <c r="E19" t="n">
-        <v>37.18</v>
+        <v>48.33</v>
       </c>
       <c r="F19" t="n">
-        <v>37.35</v>
+        <v>49.26</v>
       </c>
       <c r="G19" t="n">
-        <v>37.33</v>
+        <v>50.7</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.197</v>
+        <v>-1.707</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.049</v>
+        <v>-1.371</v>
       </c>
       <c r="J19" t="n">
-        <v>33.91</v>
+        <v>18.9</v>
       </c>
       <c r="K19" t="n">
-        <v>46.63</v>
+        <v>25.09</v>
       </c>
       <c r="L19" t="n">
-        <v>8.470000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="M19" t="n">
-        <v>35.22</v>
+        <v>37.47</v>
       </c>
       <c r="N19" t="n">
-        <v>43.19</v>
+        <v>40.77</v>
       </c>
       <c r="O19" t="n">
-        <v>47.46</v>
+        <v>44.95</v>
       </c>
       <c r="P19" t="n">
-        <v>3990.09</v>
+        <v>3817.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>5992.46</v>
+        <v>6283.44</v>
       </c>
       <c r="R19" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="S19" t="n">
-        <v>36.65</v>
+        <v>46.5</v>
       </c>
       <c r="T19" t="n">
-        <v>37</v>
+        <v>48.24</v>
       </c>
       <c r="U19" t="n">
-        <v>35.6</v>
+        <v>46.2</v>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
@@ -1849,69 +1849,69 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>300017</v>
+        <v>2230</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.05</v>
+        <v>45.58</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.02</v>
+        <v>-0.31</v>
       </c>
       <c r="E20" t="n">
-        <v>16.76</v>
+        <v>46.08</v>
       </c>
       <c r="F20" t="n">
-        <v>17.13</v>
+        <v>46.45</v>
       </c>
       <c r="G20" t="n">
-        <v>17.67</v>
+        <v>48.83</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.314</v>
+        <v>-2.215</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.074</v>
+        <v>-2.124</v>
       </c>
       <c r="J20" t="n">
-        <v>15.05</v>
+        <v>14.27</v>
       </c>
       <c r="K20" t="n">
-        <v>23.88</v>
+        <v>16.34</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6</v>
+        <v>10.12</v>
       </c>
       <c r="M20" t="n">
-        <v>31.98</v>
+        <v>25.93</v>
       </c>
       <c r="N20" t="n">
-        <v>40.06</v>
+        <v>27.96</v>
       </c>
       <c r="O20" t="n">
-        <v>47.28</v>
+        <v>34.51</v>
       </c>
       <c r="P20" t="n">
-        <v>14241.37</v>
+        <v>1706.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>24656.41</v>
+        <v>3040.34</v>
       </c>
       <c r="R20" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>16.49</v>
+        <v>45.75</v>
       </c>
       <c r="T20" t="n">
-        <v>16.69</v>
+        <v>45.99</v>
       </c>
       <c r="U20" t="n">
-        <v>15.95</v>
+        <v>45.38</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
@@ -1922,69 +1922,69 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>300418</v>
+        <v>300058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>47.22</v>
+        <v>13.59</v>
       </c>
       <c r="D21" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="E21" t="n">
-        <v>48.33</v>
+        <v>14.04</v>
       </c>
       <c r="F21" t="n">
-        <v>49.26</v>
+        <v>14.13</v>
       </c>
       <c r="G21" t="n">
-        <v>50.7</v>
+        <v>14.71</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.707</v>
+        <v>-0.873</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.371</v>
+        <v>-0.871</v>
       </c>
       <c r="J21" t="n">
-        <v>18.9</v>
+        <v>23.46</v>
       </c>
       <c r="K21" t="n">
-        <v>25.09</v>
+        <v>30.89</v>
       </c>
       <c r="L21" t="n">
-        <v>6.52</v>
+        <v>8.59</v>
       </c>
       <c r="M21" t="n">
-        <v>37.47</v>
+        <v>33.91</v>
       </c>
       <c r="N21" t="n">
-        <v>40.77</v>
+        <v>35.75</v>
       </c>
       <c r="O21" t="n">
-        <v>44.95</v>
+        <v>42.25</v>
       </c>
       <c r="P21" t="n">
-        <v>3817.4</v>
+        <v>17304.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>6283.44</v>
+        <v>26127.22</v>
       </c>
       <c r="R21" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="S21" t="n">
-        <v>46.5</v>
+        <v>13.58</v>
       </c>
       <c r="T21" t="n">
-        <v>48.24</v>
+        <v>13.85</v>
       </c>
       <c r="U21" t="n">
-        <v>46.2</v>
+        <v>13.34</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
@@ -1995,69 +1995,69 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2230</v>
+        <v>300496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.58</v>
+        <v>56.73</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="E22" t="n">
-        <v>46.08</v>
+        <v>57.81</v>
       </c>
       <c r="F22" t="n">
-        <v>46.45</v>
+        <v>58.82</v>
       </c>
       <c r="G22" t="n">
-        <v>48.83</v>
+        <v>62.61</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.215</v>
+        <v>-3.398</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.124</v>
+        <v>-3.1</v>
       </c>
       <c r="J22" t="n">
-        <v>14.27</v>
+        <v>7.78</v>
       </c>
       <c r="K22" t="n">
-        <v>16.34</v>
+        <v>11.48</v>
       </c>
       <c r="L22" t="n">
-        <v>10.12</v>
+        <v>0.37</v>
       </c>
       <c r="M22" t="n">
-        <v>25.93</v>
+        <v>20.63</v>
       </c>
       <c r="N22" t="n">
-        <v>27.96</v>
+        <v>25.75</v>
       </c>
       <c r="O22" t="n">
-        <v>34.51</v>
+        <v>33.12</v>
       </c>
       <c r="P22" t="n">
-        <v>1706.7</v>
+        <v>662.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3040.34</v>
+        <v>1125.09</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="S22" t="n">
-        <v>45.75</v>
+        <v>56.89</v>
       </c>
       <c r="T22" t="n">
-        <v>45.99</v>
+        <v>57.79</v>
       </c>
       <c r="U22" t="n">
-        <v>45.38</v>
+        <v>56.59</v>
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
@@ -2068,69 +2068,69 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>300058</v>
+        <v>547</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>航天发展</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.59</v>
+        <v>25.93</v>
       </c>
       <c r="D23" t="n">
-        <v>1.65</v>
+        <v>0.58</v>
       </c>
       <c r="E23" t="n">
-        <v>14.04</v>
+        <v>27.01</v>
       </c>
       <c r="F23" t="n">
-        <v>14.13</v>
+        <v>27.32</v>
       </c>
       <c r="G23" t="n">
-        <v>14.71</v>
+        <v>29.06</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.873</v>
+        <v>-0.983</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.871</v>
+        <v>-0.655</v>
       </c>
       <c r="J23" t="n">
-        <v>23.46</v>
+        <v>27.5</v>
       </c>
       <c r="K23" t="n">
-        <v>30.89</v>
+        <v>35.96</v>
       </c>
       <c r="L23" t="n">
-        <v>8.59</v>
+        <v>10.57</v>
       </c>
       <c r="M23" t="n">
-        <v>33.91</v>
+        <v>30.08</v>
       </c>
       <c r="N23" t="n">
-        <v>35.75</v>
+        <v>37.52</v>
       </c>
       <c r="O23" t="n">
-        <v>42.25</v>
+        <v>43.88</v>
       </c>
       <c r="P23" t="n">
-        <v>17304.69</v>
+        <v>10264.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>26127.22</v>
+        <v>20699.82</v>
       </c>
       <c r="R23" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="S23" t="n">
-        <v>13.58</v>
+        <v>25.77</v>
       </c>
       <c r="T23" t="n">
-        <v>13.85</v>
+        <v>26.28</v>
       </c>
       <c r="U23" t="n">
-        <v>13.34</v>
+        <v>25.57</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
@@ -2141,69 +2141,69 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>300496</v>
+        <v>2202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56.73</v>
+        <v>22.89</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.26</v>
+        <v>-5.49</v>
       </c>
       <c r="E24" t="n">
-        <v>57.81</v>
+        <v>24.57</v>
       </c>
       <c r="F24" t="n">
-        <v>58.82</v>
+        <v>26.2</v>
       </c>
       <c r="G24" t="n">
-        <v>62.61</v>
+        <v>28.02</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.398</v>
+        <v>-0.923</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.1</v>
+        <v>-0.193</v>
       </c>
       <c r="J24" t="n">
-        <v>7.78</v>
+        <v>8.93</v>
       </c>
       <c r="K24" t="n">
-        <v>11.48</v>
+        <v>11.74</v>
       </c>
       <c r="L24" t="n">
-        <v>0.37</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>20.63</v>
+        <v>16.58</v>
       </c>
       <c r="N24" t="n">
-        <v>25.75</v>
+        <v>29.71</v>
       </c>
       <c r="O24" t="n">
-        <v>33.12</v>
+        <v>41.11</v>
       </c>
       <c r="P24" t="n">
-        <v>662.03</v>
+        <v>22857.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>1125.09</v>
+        <v>28391.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.59</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>56.89</v>
+        <v>23.84</v>
       </c>
       <c r="T24" t="n">
-        <v>57.79</v>
+        <v>23.84</v>
       </c>
       <c r="U24" t="n">
-        <v>56.59</v>
+        <v>22.8</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
@@ -2214,69 +2214,69 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>547</v>
+        <v>301128</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.93</v>
+        <v>147.19</v>
       </c>
       <c r="D25" t="n">
-        <v>0.58</v>
+        <v>-5.04</v>
       </c>
       <c r="E25" t="n">
-        <v>27.01</v>
+        <v>150.81</v>
       </c>
       <c r="F25" t="n">
-        <v>27.32</v>
+        <v>144.18</v>
       </c>
       <c r="G25" t="n">
-        <v>29.06</v>
+        <v>131.14</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.983</v>
+        <v>11.128</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.655</v>
+        <v>9.500999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>27.5</v>
+        <v>70.97</v>
       </c>
       <c r="K25" t="n">
-        <v>35.96</v>
+        <v>76.77</v>
       </c>
       <c r="L25" t="n">
-        <v>10.57</v>
+        <v>59.36</v>
       </c>
       <c r="M25" t="n">
-        <v>30.08</v>
+        <v>58.26</v>
       </c>
       <c r="N25" t="n">
-        <v>37.52</v>
+        <v>63.12</v>
       </c>
       <c r="O25" t="n">
-        <v>43.88</v>
+        <v>62.99</v>
       </c>
       <c r="P25" t="n">
-        <v>10264.6</v>
+        <v>697.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>20699.82</v>
+        <v>906.05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="S25" t="n">
-        <v>25.77</v>
+        <v>155.02</v>
       </c>
       <c r="T25" t="n">
-        <v>26.28</v>
+        <v>156</v>
       </c>
       <c r="U25" t="n">
-        <v>25.57</v>
+        <v>144.8</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
@@ -2287,69 +2287,69 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2202</v>
+        <v>601899</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.89</v>
+        <v>32.41</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.49</v>
+        <v>-1.52</v>
       </c>
       <c r="E26" t="n">
-        <v>24.57</v>
+        <v>33.06</v>
       </c>
       <c r="F26" t="n">
-        <v>26.2</v>
+        <v>32.81</v>
       </c>
       <c r="G26" t="n">
-        <v>28.02</v>
+        <v>33.7</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.923</v>
+        <v>-1.155</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.193</v>
+        <v>-1.265</v>
       </c>
       <c r="J26" t="n">
-        <v>8.93</v>
+        <v>51.62</v>
       </c>
       <c r="K26" t="n">
-        <v>11.74</v>
+        <v>55.47</v>
       </c>
       <c r="L26" t="n">
-        <v>3.3</v>
+        <v>43.92</v>
       </c>
       <c r="M26" t="n">
-        <v>16.58</v>
+        <v>40.37</v>
       </c>
       <c r="N26" t="n">
-        <v>29.71</v>
+        <v>40.17</v>
       </c>
       <c r="O26" t="n">
-        <v>41.11</v>
+        <v>42.77</v>
       </c>
       <c r="P26" t="n">
-        <v>22857.68</v>
+        <v>15064.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>28391.1</v>
+        <v>29017.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="S26" t="n">
-        <v>23.84</v>
+        <v>32.8</v>
       </c>
       <c r="T26" t="n">
-        <v>23.84</v>
+        <v>33.1</v>
       </c>
       <c r="U26" t="n">
-        <v>22.8</v>
+        <v>32.33</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
@@ -2360,69 +2360,69 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>301128</v>
+        <v>600219</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>147.19</v>
+        <v>6.09</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.04</v>
+        <v>2.53</v>
       </c>
       <c r="E27" t="n">
-        <v>150.81</v>
+        <v>6.1</v>
       </c>
       <c r="F27" t="n">
-        <v>144.18</v>
+        <v>6.08</v>
       </c>
       <c r="G27" t="n">
-        <v>131.14</v>
+        <v>6.45</v>
       </c>
       <c r="H27" t="n">
-        <v>11.128</v>
+        <v>-0.229</v>
       </c>
       <c r="I27" t="n">
-        <v>9.500999999999999</v>
+        <v>-0.204</v>
       </c>
       <c r="J27" t="n">
-        <v>70.97</v>
+        <v>41.26</v>
       </c>
       <c r="K27" t="n">
-        <v>76.77</v>
+        <v>39.82</v>
       </c>
       <c r="L27" t="n">
-        <v>59.36</v>
+        <v>44.13</v>
       </c>
       <c r="M27" t="n">
-        <v>58.26</v>
+        <v>45.15</v>
       </c>
       <c r="N27" t="n">
-        <v>63.12</v>
+        <v>42.93</v>
       </c>
       <c r="O27" t="n">
-        <v>62.99</v>
+        <v>45.94</v>
       </c>
       <c r="P27" t="n">
-        <v>697.36</v>
+        <v>19086.53</v>
       </c>
       <c r="Q27" t="n">
-        <v>906.05</v>
+        <v>27202.59</v>
       </c>
       <c r="R27" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="S27" t="n">
-        <v>155.02</v>
+        <v>5.95</v>
       </c>
       <c r="T27" t="n">
-        <v>156</v>
+        <v>6.15</v>
       </c>
       <c r="U27" t="n">
-        <v>144.8</v>
+        <v>5.8</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
@@ -2433,69 +2433,69 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>601899</v>
+        <v>601939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.52</v>
+        <v>-2.02</v>
       </c>
       <c r="E28" t="n">
-        <v>33.06</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>32.81</v>
+        <v>9.44</v>
       </c>
       <c r="G28" t="n">
-        <v>33.7</v>
+        <v>9.31</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.155</v>
+        <v>0.125</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.265</v>
+        <v>0.139</v>
       </c>
       <c r="J28" t="n">
-        <v>51.62</v>
+        <v>49.22</v>
       </c>
       <c r="K28" t="n">
-        <v>55.47</v>
+        <v>68.27</v>
       </c>
       <c r="L28" t="n">
-        <v>43.92</v>
+        <v>11.12</v>
       </c>
       <c r="M28" t="n">
-        <v>40.37</v>
+        <v>37.06</v>
       </c>
       <c r="N28" t="n">
-        <v>40.17</v>
+        <v>47.33</v>
       </c>
       <c r="O28" t="n">
-        <v>42.77</v>
+        <v>51.49</v>
       </c>
       <c r="P28" t="n">
-        <v>15064.98</v>
+        <v>8028.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>29017.8</v>
+        <v>9730.09</v>
       </c>
       <c r="R28" t="n">
-        <v>0.52</v>
+        <v>0.83</v>
       </c>
       <c r="S28" t="n">
-        <v>32.8</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>33.1</v>
+        <v>9.4</v>
       </c>
       <c r="U28" t="n">
-        <v>32.33</v>
+        <v>9.18</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
@@ -2506,69 +2506,69 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>600219</v>
+        <v>600048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>保利发展</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.09</v>
+        <v>5.5</v>
       </c>
       <c r="D29" t="n">
-        <v>2.53</v>
+        <v>-0.18</v>
       </c>
       <c r="E29" t="n">
-        <v>6.1</v>
+        <v>5.68</v>
       </c>
       <c r="F29" t="n">
-        <v>6.08</v>
+        <v>5.8</v>
       </c>
       <c r="G29" t="n">
-        <v>6.45</v>
+        <v>6.06</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.229</v>
+        <v>-0.255</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.204</v>
+        <v>-0.208</v>
       </c>
       <c r="J29" t="n">
-        <v>41.26</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>39.82</v>
+        <v>9.06</v>
       </c>
       <c r="L29" t="n">
-        <v>44.13</v>
+        <v>2.87</v>
       </c>
       <c r="M29" t="n">
-        <v>45.15</v>
+        <v>14.01</v>
       </c>
       <c r="N29" t="n">
-        <v>42.93</v>
+        <v>20.92</v>
       </c>
       <c r="O29" t="n">
-        <v>45.94</v>
+        <v>31.08</v>
       </c>
       <c r="P29" t="n">
-        <v>19086.53</v>
+        <v>6653.44</v>
       </c>
       <c r="Q29" t="n">
-        <v>27202.59</v>
+        <v>10863.94</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="S29" t="n">
-        <v>5.95</v>
+        <v>5.51</v>
       </c>
       <c r="T29" t="n">
-        <v>6.15</v>
+        <v>5.55</v>
       </c>
       <c r="U29" t="n">
-        <v>5.8</v>
+        <v>5.47</v>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
@@ -2579,69 +2579,69 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>601939</v>
+        <v>600941</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.210000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.02</v>
+        <v>0.39</v>
       </c>
       <c r="E30" t="n">
-        <v>9.460000000000001</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>9.44</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>9.31</v>
+        <v>95.17</v>
       </c>
       <c r="H30" t="n">
-        <v>0.125</v>
+        <v>-0.714</v>
       </c>
       <c r="I30" t="n">
-        <v>0.139</v>
+        <v>-0.511</v>
       </c>
       <c r="J30" t="n">
-        <v>49.22</v>
+        <v>34.47</v>
       </c>
       <c r="K30" t="n">
-        <v>68.27</v>
+        <v>27.85</v>
       </c>
       <c r="L30" t="n">
-        <v>11.12</v>
+        <v>47.72</v>
       </c>
       <c r="M30" t="n">
-        <v>37.06</v>
+        <v>37.6</v>
       </c>
       <c r="N30" t="n">
-        <v>47.33</v>
+        <v>40.21</v>
       </c>
       <c r="O30" t="n">
-        <v>51.49</v>
+        <v>42.08</v>
       </c>
       <c r="P30" t="n">
-        <v>8028.77</v>
+        <v>547.23</v>
       </c>
       <c r="Q30" t="n">
-        <v>9730.09</v>
+        <v>988.5700000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="S30" t="n">
-        <v>9.390000000000001</v>
+        <v>93.03</v>
       </c>
       <c r="T30" t="n">
-        <v>9.4</v>
+        <v>93.53</v>
       </c>
       <c r="U30" t="n">
-        <v>9.18</v>
+        <v>92.94</v>
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
@@ -2652,69 +2652,69 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>600048</v>
+        <v>2352</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>保利发展</t>
+          <t>顺丰控股</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.5</v>
+        <v>37.79</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.18</v>
+        <v>0.48</v>
       </c>
       <c r="E31" t="n">
-        <v>5.68</v>
+        <v>37.93</v>
       </c>
       <c r="F31" t="n">
-        <v>5.8</v>
+        <v>37.23</v>
       </c>
       <c r="G31" t="n">
-        <v>6.06</v>
+        <v>37.17</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.255</v>
+        <v>0.045</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.208</v>
+        <v>-0.142</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>9.06</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>2.87</v>
+        <v>79.39</v>
       </c>
       <c r="M31" t="n">
-        <v>14.01</v>
+        <v>59.1</v>
       </c>
       <c r="N31" t="n">
-        <v>20.92</v>
+        <v>54.94</v>
       </c>
       <c r="O31" t="n">
-        <v>31.08</v>
+        <v>51.43</v>
       </c>
       <c r="P31" t="n">
-        <v>6653.44</v>
+        <v>1964.37</v>
       </c>
       <c r="Q31" t="n">
-        <v>10863.94</v>
+        <v>2268.37</v>
       </c>
       <c r="R31" t="n">
-        <v>0.61</v>
+        <v>0.87</v>
       </c>
       <c r="S31" t="n">
-        <v>5.51</v>
+        <v>37.55</v>
       </c>
       <c r="T31" t="n">
-        <v>5.55</v>
+        <v>37.84</v>
       </c>
       <c r="U31" t="n">
-        <v>5.47</v>
+        <v>37.34</v>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
@@ -2725,69 +2725,69 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>600941</v>
+        <v>603803</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.38</v>
+        <v>13.13</v>
       </c>
       <c r="D32" t="n">
-        <v>0.39</v>
+        <v>-0.61</v>
       </c>
       <c r="E32" t="n">
-        <v>93.45999999999999</v>
+        <v>13.14</v>
       </c>
       <c r="F32" t="n">
-        <v>93.56999999999999</v>
+        <v>13.85</v>
       </c>
       <c r="G32" t="n">
-        <v>95.17</v>
+        <v>13.38</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.714</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.511</v>
+        <v>0.751</v>
       </c>
       <c r="J32" t="n">
-        <v>34.47</v>
+        <v>26.07</v>
       </c>
       <c r="K32" t="n">
-        <v>27.85</v>
+        <v>35.04</v>
       </c>
       <c r="L32" t="n">
-        <v>47.72</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>37.6</v>
+        <v>45.26</v>
       </c>
       <c r="N32" t="n">
-        <v>40.21</v>
+        <v>51.56</v>
       </c>
       <c r="O32" t="n">
-        <v>42.08</v>
+        <v>54.13</v>
       </c>
       <c r="P32" t="n">
-        <v>547.23</v>
+        <v>5773.74</v>
       </c>
       <c r="Q32" t="n">
-        <v>988.5700000000001</v>
+        <v>8931.66</v>
       </c>
       <c r="R32" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="S32" t="n">
-        <v>93.03</v>
+        <v>12.89</v>
       </c>
       <c r="T32" t="n">
-        <v>93.53</v>
+        <v>13.72</v>
       </c>
       <c r="U32" t="n">
-        <v>92.94</v>
+        <v>12.89</v>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
@@ -2798,69 +2798,69 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2352</v>
+        <v>2624</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.79</v>
+        <v>19.58</v>
       </c>
       <c r="D33" t="n">
-        <v>0.48</v>
+        <v>1.93</v>
       </c>
       <c r="E33" t="n">
-        <v>37.93</v>
+        <v>19.06</v>
       </c>
       <c r="F33" t="n">
-        <v>37.23</v>
+        <v>18.51</v>
       </c>
       <c r="G33" t="n">
-        <v>37.17</v>
+        <v>18.87</v>
       </c>
       <c r="H33" t="n">
-        <v>0.045</v>
+        <v>-0.145</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.142</v>
+        <v>-0.292</v>
       </c>
       <c r="J33" t="n">
-        <v>72.34999999999999</v>
+        <v>70.84</v>
       </c>
       <c r="K33" t="n">
-        <v>68.81999999999999</v>
+        <v>60.96</v>
       </c>
       <c r="L33" t="n">
-        <v>79.39</v>
+        <v>90.58</v>
       </c>
       <c r="M33" t="n">
-        <v>59.1</v>
+        <v>64.36</v>
       </c>
       <c r="N33" t="n">
-        <v>54.94</v>
+        <v>55.49</v>
       </c>
       <c r="O33" t="n">
-        <v>51.43</v>
+        <v>53.52</v>
       </c>
       <c r="P33" t="n">
-        <v>1964.37</v>
+        <v>5401.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>2268.37</v>
+        <v>5323.28</v>
       </c>
       <c r="R33" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="S33" t="n">
-        <v>37.55</v>
+        <v>19.5</v>
       </c>
       <c r="T33" t="n">
-        <v>37.84</v>
+        <v>19.74</v>
       </c>
       <c r="U33" t="n">
-        <v>37.34</v>
+        <v>19.3</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
@@ -2871,69 +2871,69 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603803</v>
+        <v>2558</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13.13</v>
+        <v>32.91</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.61</v>
+        <v>-0.87</v>
       </c>
       <c r="E34" t="n">
-        <v>13.14</v>
+        <v>33.28</v>
       </c>
       <c r="F34" t="n">
-        <v>13.85</v>
+        <v>32.58</v>
       </c>
       <c r="G34" t="n">
-        <v>13.38</v>
+        <v>33.52</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5639999999999999</v>
+        <v>-1.428</v>
       </c>
       <c r="I34" t="n">
-        <v>0.751</v>
+        <v>-1.852</v>
       </c>
       <c r="J34" t="n">
-        <v>26.07</v>
+        <v>51.88</v>
       </c>
       <c r="K34" t="n">
-        <v>35.04</v>
+        <v>46.21</v>
       </c>
       <c r="L34" t="n">
-        <v>8.140000000000001</v>
+        <v>63.21</v>
       </c>
       <c r="M34" t="n">
-        <v>45.26</v>
+        <v>47.87</v>
       </c>
       <c r="N34" t="n">
-        <v>51.56</v>
+        <v>42.89</v>
       </c>
       <c r="O34" t="n">
-        <v>54.13</v>
+        <v>40.04</v>
       </c>
       <c r="P34" t="n">
-        <v>5773.74</v>
+        <v>4204.01</v>
       </c>
       <c r="Q34" t="n">
-        <v>8931.66</v>
+        <v>4165.23</v>
       </c>
       <c r="R34" t="n">
-        <v>0.65</v>
+        <v>1.01</v>
       </c>
       <c r="S34" t="n">
-        <v>12.89</v>
+        <v>33.24</v>
       </c>
       <c r="T34" t="n">
-        <v>13.72</v>
+        <v>33.71</v>
       </c>
       <c r="U34" t="n">
-        <v>12.89</v>
+        <v>32.55</v>
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
@@ -2944,69 +2944,69 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2624</v>
+        <v>601088</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>完美世界</t>
+          <t>中国神华</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19.58</v>
+        <v>48.42</v>
       </c>
       <c r="D35" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="E35" t="n">
-        <v>19.06</v>
+        <v>47.41</v>
       </c>
       <c r="F35" t="n">
-        <v>18.51</v>
+        <v>47.58</v>
       </c>
       <c r="G35" t="n">
-        <v>18.87</v>
+        <v>48.01</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.145</v>
+        <v>0.759</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.292</v>
+        <v>1.025</v>
       </c>
       <c r="J35" t="n">
-        <v>70.84</v>
+        <v>54.96</v>
       </c>
       <c r="K35" t="n">
-        <v>60.96</v>
+        <v>40.48</v>
       </c>
       <c r="L35" t="n">
-        <v>90.58</v>
+        <v>83.94</v>
       </c>
       <c r="M35" t="n">
-        <v>64.36</v>
+        <v>61.57</v>
       </c>
       <c r="N35" t="n">
-        <v>55.49</v>
+        <v>58.6</v>
       </c>
       <c r="O35" t="n">
-        <v>53.52</v>
+        <v>59.03</v>
       </c>
       <c r="P35" t="n">
-        <v>5401.71</v>
+        <v>2643.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>5323.28</v>
+        <v>4027.74</v>
       </c>
       <c r="R35" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="S35" t="n">
-        <v>19.5</v>
+        <v>47.58</v>
       </c>
       <c r="T35" t="n">
-        <v>19.74</v>
+        <v>48.59</v>
       </c>
       <c r="U35" t="n">
-        <v>19.3</v>
+        <v>47.22</v>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
@@ -3017,69 +3017,69 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2558</v>
+        <v>600963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>岳阳林纸</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32.91</v>
+        <v>4.71</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.87</v>
+        <v>0.64</v>
       </c>
       <c r="E36" t="n">
-        <v>33.28</v>
+        <v>4.74</v>
       </c>
       <c r="F36" t="n">
-        <v>32.58</v>
+        <v>4.75</v>
       </c>
       <c r="G36" t="n">
-        <v>33.52</v>
+        <v>5.07</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.428</v>
+        <v>-0.247</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.852</v>
+        <v>-0.222</v>
       </c>
       <c r="J36" t="n">
-        <v>51.88</v>
+        <v>37.91</v>
       </c>
       <c r="K36" t="n">
-        <v>46.21</v>
+        <v>36.2</v>
       </c>
       <c r="L36" t="n">
-        <v>63.21</v>
+        <v>41.33</v>
       </c>
       <c r="M36" t="n">
-        <v>47.87</v>
+        <v>37.38</v>
       </c>
       <c r="N36" t="n">
-        <v>42.89</v>
+        <v>36.55</v>
       </c>
       <c r="O36" t="n">
-        <v>40.04</v>
+        <v>41.84</v>
       </c>
       <c r="P36" t="n">
-        <v>4204.01</v>
+        <v>1721.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>4165.23</v>
+        <v>3972.78</v>
       </c>
       <c r="R36" t="n">
-        <v>1.01</v>
+        <v>0.43</v>
       </c>
       <c r="S36" t="n">
-        <v>33.24</v>
+        <v>4.65</v>
       </c>
       <c r="T36" t="n">
-        <v>33.71</v>
+        <v>4.77</v>
       </c>
       <c r="U36" t="n">
-        <v>32.55</v>
+        <v>4.6</v>
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
@@ -3090,69 +3090,69 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>601088</v>
+        <v>601877</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.42</v>
+        <v>31.46</v>
       </c>
       <c r="D37" t="n">
-        <v>1.77</v>
+        <v>0.87</v>
       </c>
       <c r="E37" t="n">
-        <v>47.41</v>
+        <v>31.98</v>
       </c>
       <c r="F37" t="n">
-        <v>47.58</v>
+        <v>33.17</v>
       </c>
       <c r="G37" t="n">
-        <v>48.01</v>
+        <v>35.13</v>
       </c>
       <c r="H37" t="n">
-        <v>0.759</v>
+        <v>-0.544</v>
       </c>
       <c r="I37" t="n">
-        <v>1.025</v>
+        <v>0.089</v>
       </c>
       <c r="J37" t="n">
-        <v>54.96</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>40.48</v>
+        <v>13.43</v>
       </c>
       <c r="L37" t="n">
-        <v>83.94</v>
+        <v>3.15</v>
       </c>
       <c r="M37" t="n">
-        <v>61.57</v>
+        <v>25.21</v>
       </c>
       <c r="N37" t="n">
-        <v>58.6</v>
+        <v>36.41</v>
       </c>
       <c r="O37" t="n">
-        <v>59.03</v>
+        <v>45.02</v>
       </c>
       <c r="P37" t="n">
-        <v>2643.6</v>
+        <v>1845.86</v>
       </c>
       <c r="Q37" t="n">
-        <v>4027.74</v>
+        <v>5114.17</v>
       </c>
       <c r="R37" t="n">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="S37" t="n">
-        <v>47.58</v>
+        <v>31.08</v>
       </c>
       <c r="T37" t="n">
-        <v>48.59</v>
+        <v>31.57</v>
       </c>
       <c r="U37" t="n">
-        <v>47.22</v>
+        <v>30.91</v>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
@@ -3163,69 +3163,69 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>600963</v>
+        <v>2049</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>岳阳林纸</t>
+          <t>紫光国微</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.71</v>
+        <v>65.58</v>
       </c>
       <c r="D38" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="E38" t="n">
-        <v>4.74</v>
+        <v>65.97</v>
       </c>
       <c r="F38" t="n">
-        <v>4.75</v>
+        <v>66.95</v>
       </c>
       <c r="G38" t="n">
-        <v>5.07</v>
+        <v>70.02</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.247</v>
+        <v>-2.972</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.222</v>
+        <v>-2.769</v>
       </c>
       <c r="J38" t="n">
-        <v>37.91</v>
+        <v>12.95</v>
       </c>
       <c r="K38" t="n">
-        <v>36.2</v>
+        <v>14.16</v>
       </c>
       <c r="L38" t="n">
-        <v>41.33</v>
+        <v>10.51</v>
       </c>
       <c r="M38" t="n">
-        <v>37.38</v>
+        <v>34.1</v>
       </c>
       <c r="N38" t="n">
-        <v>36.55</v>
+        <v>33.82</v>
       </c>
       <c r="O38" t="n">
-        <v>41.84</v>
+        <v>37.08</v>
       </c>
       <c r="P38" t="n">
-        <v>1721.08</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>3972.78</v>
+        <v>1224.33</v>
       </c>
       <c r="R38" t="n">
-        <v>0.43</v>
+        <v>0.68</v>
       </c>
       <c r="S38" t="n">
-        <v>4.65</v>
+        <v>65</v>
       </c>
       <c r="T38" t="n">
-        <v>4.77</v>
+        <v>66.17</v>
       </c>
       <c r="U38" t="n">
-        <v>4.6</v>
+        <v>65</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
@@ -3236,69 +3236,69 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>601877</v>
+        <v>601689</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>31.46</v>
+        <v>56.27</v>
       </c>
       <c r="D39" t="n">
-        <v>0.87</v>
+        <v>-2.39</v>
       </c>
       <c r="E39" t="n">
-        <v>31.98</v>
+        <v>57.61</v>
       </c>
       <c r="F39" t="n">
-        <v>33.17</v>
+        <v>57.63</v>
       </c>
       <c r="G39" t="n">
-        <v>35.13</v>
+        <v>59.71</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.544</v>
+        <v>-2.667</v>
       </c>
       <c r="I39" t="n">
-        <v>0.089</v>
+        <v>-2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>10</v>
+        <v>34.77</v>
       </c>
       <c r="K39" t="n">
-        <v>13.43</v>
+        <v>38.79</v>
       </c>
       <c r="L39" t="n">
-        <v>3.15</v>
+        <v>26.73</v>
       </c>
       <c r="M39" t="n">
-        <v>25.21</v>
+        <v>27.99</v>
       </c>
       <c r="N39" t="n">
-        <v>36.41</v>
+        <v>28.67</v>
       </c>
       <c r="O39" t="n">
-        <v>45.02</v>
+        <v>32.82</v>
       </c>
       <c r="P39" t="n">
-        <v>1845.86</v>
+        <v>2026.29</v>
       </c>
       <c r="Q39" t="n">
-        <v>5114.17</v>
+        <v>2239.06</v>
       </c>
       <c r="R39" t="n">
-        <v>0.36</v>
+        <v>0.9</v>
       </c>
       <c r="S39" t="n">
-        <v>31.08</v>
+        <v>57.58</v>
       </c>
       <c r="T39" t="n">
-        <v>31.57</v>
+        <v>57.65</v>
       </c>
       <c r="U39" t="n">
-        <v>30.91</v>
+        <v>55.95</v>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
@@ -3309,69 +3309,69 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>紫光国微</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>65.58</v>
+        <v>41.77</v>
       </c>
       <c r="D40" t="n">
-        <v>1.02</v>
+        <v>-0.31</v>
       </c>
       <c r="E40" t="n">
-        <v>65.97</v>
+        <v>42.52</v>
       </c>
       <c r="F40" t="n">
-        <v>66.95</v>
+        <v>42.89</v>
       </c>
       <c r="G40" t="n">
-        <v>70.02</v>
+        <v>44.64</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.972</v>
+        <v>-1.906</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.769</v>
+        <v>-1.879</v>
       </c>
       <c r="J40" t="n">
-        <v>12.95</v>
+        <v>26.17</v>
       </c>
       <c r="K40" t="n">
-        <v>14.16</v>
+        <v>31.97</v>
       </c>
       <c r="L40" t="n">
-        <v>10.51</v>
+        <v>14.55</v>
       </c>
       <c r="M40" t="n">
-        <v>34.1</v>
+        <v>27.91</v>
       </c>
       <c r="N40" t="n">
-        <v>33.82</v>
+        <v>30.77</v>
       </c>
       <c r="O40" t="n">
-        <v>37.08</v>
+        <v>36.2</v>
       </c>
       <c r="P40" t="n">
-        <v>834.0700000000001</v>
+        <v>3992.93</v>
       </c>
       <c r="Q40" t="n">
-        <v>1224.33</v>
+        <v>7035.29</v>
       </c>
       <c r="R40" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="S40" t="n">
-        <v>65</v>
+        <v>41.9</v>
       </c>
       <c r="T40" t="n">
-        <v>66.17</v>
+        <v>42.25</v>
       </c>
       <c r="U40" t="n">
-        <v>65</v>
+        <v>41.4</v>
       </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
@@ -3382,69 +3382,69 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>688271</v>
+        <v>887</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>联影医疗</t>
+          <t>中鼎股份</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>109.6</v>
+        <v>17.46</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.03</v>
+        <v>-0.74</v>
       </c>
       <c r="E41" t="n">
-        <v>112.58</v>
+        <v>17.85</v>
       </c>
       <c r="F41" t="n">
-        <v>112.82</v>
+        <v>17.95</v>
       </c>
       <c r="G41" t="n">
-        <v>115.64</v>
+        <v>18.51</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.493</v>
+        <v>-0.741</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.555</v>
+        <v>-0.758</v>
       </c>
       <c r="J41" t="n">
-        <v>34.68</v>
+        <v>30.57</v>
       </c>
       <c r="K41" t="n">
-        <v>38.15</v>
+        <v>36.96</v>
       </c>
       <c r="L41" t="n">
-        <v>27.75</v>
+        <v>17.8</v>
       </c>
       <c r="M41" t="n">
-        <v>28.23</v>
+        <v>27.96</v>
       </c>
       <c r="N41" t="n">
-        <v>31.37</v>
+        <v>29.96</v>
       </c>
       <c r="O41" t="n">
-        <v>34.73</v>
+        <v>32.6</v>
       </c>
       <c r="P41" t="n">
-        <v>372.15</v>
+        <v>920.77</v>
       </c>
       <c r="Q41" t="n">
-        <v>378.33</v>
+        <v>1638.27</v>
       </c>
       <c r="R41" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S41" t="n">
-        <v>112</v>
+        <v>17.6</v>
       </c>
       <c r="T41" t="n">
-        <v>112.45</v>
+        <v>17.72</v>
       </c>
       <c r="U41" t="n">
-        <v>109.01</v>
+        <v>17.36</v>
       </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
@@ -3455,69 +3455,69 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>688608</v>
+        <v>603236</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>恒玄科技</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>161.8</v>
+        <v>72.58</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.06</v>
+        <v>-1.24</v>
       </c>
       <c r="E42" t="n">
-        <v>167.96</v>
+        <v>73.47</v>
       </c>
       <c r="F42" t="n">
-        <v>165.78</v>
+        <v>73.39</v>
       </c>
       <c r="G42" t="n">
-        <v>171.06</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>-8.861000000000001</v>
+        <v>-3.039</v>
       </c>
       <c r="I42" t="n">
-        <v>-10.044</v>
+        <v>-3.286</v>
       </c>
       <c r="J42" t="n">
-        <v>35.58</v>
+        <v>35.52</v>
       </c>
       <c r="K42" t="n">
-        <v>40.75</v>
+        <v>32.51</v>
       </c>
       <c r="L42" t="n">
-        <v>25.26</v>
+        <v>41.53</v>
       </c>
       <c r="M42" t="n">
-        <v>35.98</v>
+        <v>37.69</v>
       </c>
       <c r="N42" t="n">
-        <v>35.81</v>
+        <v>34.84</v>
       </c>
       <c r="O42" t="n">
-        <v>36.37</v>
+        <v>35.08</v>
       </c>
       <c r="P42" t="n">
-        <v>209.18</v>
+        <v>423.46</v>
       </c>
       <c r="Q42" t="n">
-        <v>302.07</v>
+        <v>486.77</v>
       </c>
       <c r="R42" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="S42" t="n">
-        <v>163</v>
+        <v>73.5</v>
       </c>
       <c r="T42" t="n">
-        <v>164.95</v>
+        <v>74.55</v>
       </c>
       <c r="U42" t="n">
-        <v>161.19</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
@@ -3528,69 +3528,69 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>688099</v>
+        <v>603072</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>晶晨股份</t>
+          <t>天和磁材</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>76</v>
+        <v>35.92</v>
       </c>
       <c r="D43" t="n">
-        <v>0.32</v>
+        <v>2.22</v>
       </c>
       <c r="E43" t="n">
-        <v>77.40000000000001</v>
+        <v>35.77</v>
       </c>
       <c r="F43" t="n">
-        <v>79.23999999999999</v>
+        <v>35.79</v>
       </c>
       <c r="G43" t="n">
-        <v>83.98999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.291</v>
+        <v>-1.616</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.404</v>
+        <v>-1.656</v>
       </c>
       <c r="J43" t="n">
-        <v>9.02</v>
+        <v>52.21</v>
       </c>
       <c r="K43" t="n">
-        <v>14.6</v>
+        <v>43.87</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.16</v>
+        <v>68.89</v>
       </c>
       <c r="M43" t="n">
-        <v>25.17</v>
+        <v>45</v>
       </c>
       <c r="N43" t="n">
-        <v>32.96</v>
+        <v>38.75</v>
       </c>
       <c r="O43" t="n">
-        <v>39.17</v>
+        <v>39.21</v>
       </c>
       <c r="P43" t="n">
-        <v>525.91</v>
+        <v>151.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>1015</v>
+        <v>220.59</v>
       </c>
       <c r="R43" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S43" t="n">
-        <v>76.48999999999999</v>
+        <v>35.44</v>
       </c>
       <c r="T43" t="n">
-        <v>77.2</v>
+        <v>36.09</v>
       </c>
       <c r="U43" t="n">
-        <v>75.78</v>
+        <v>35.14</v>
       </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
@@ -3601,69 +3601,69 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>688332</v>
+        <v>301023</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>122.79</v>
+        <v>38.38</v>
       </c>
       <c r="D44" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="E44" t="n">
-        <v>119.62</v>
+        <v>38.23</v>
       </c>
       <c r="F44" t="n">
-        <v>117.5</v>
+        <v>38.66</v>
       </c>
       <c r="G44" t="n">
-        <v>120.46</v>
+        <v>40.52</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.224</v>
+        <v>-1.781</v>
       </c>
       <c r="I44" t="n">
-        <v>-4.231</v>
+        <v>-1.701</v>
       </c>
       <c r="J44" t="n">
-        <v>76.73999999999999</v>
+        <v>25.39</v>
       </c>
       <c r="K44" t="n">
-        <v>60.24</v>
+        <v>22.54</v>
       </c>
       <c r="L44" t="n">
-        <v>109.75</v>
+        <v>31.09</v>
       </c>
       <c r="M44" t="n">
-        <v>65.59999999999999</v>
+        <v>43.37</v>
       </c>
       <c r="N44" t="n">
-        <v>51.68</v>
+        <v>39.09</v>
       </c>
       <c r="O44" t="n">
-        <v>45.84</v>
+        <v>41.66</v>
       </c>
       <c r="P44" t="n">
-        <v>173.82</v>
+        <v>175.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>130.06</v>
+        <v>127.16</v>
       </c>
       <c r="R44" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>119.12</v>
+        <v>37.09</v>
       </c>
       <c r="T44" t="n">
-        <v>123.44</v>
+        <v>38.9</v>
       </c>
       <c r="U44" t="n">
-        <v>119.12</v>
+        <v>37.06</v>
       </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
@@ -3674,69 +3674,69 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>688049</v>
+        <v>2074</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44.17</v>
+        <v>33.8</v>
       </c>
       <c r="D45" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="E45" t="n">
-        <v>44.26</v>
+        <v>34.74</v>
       </c>
       <c r="F45" t="n">
-        <v>44.65</v>
+        <v>35.95</v>
       </c>
       <c r="G45" t="n">
-        <v>46.65</v>
+        <v>36.98</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.085</v>
+        <v>-0.886</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.076</v>
+        <v>-0.504</v>
       </c>
       <c r="J45" t="n">
-        <v>24.41</v>
+        <v>13.28</v>
       </c>
       <c r="K45" t="n">
-        <v>26.05</v>
+        <v>24.06</v>
       </c>
       <c r="L45" t="n">
-        <v>21.13</v>
+        <v>-8.27</v>
       </c>
       <c r="M45" t="n">
-        <v>40.2</v>
+        <v>22.89</v>
       </c>
       <c r="N45" t="n">
-        <v>37.73</v>
+        <v>29.83</v>
       </c>
       <c r="O45" t="n">
-        <v>39.02</v>
+        <v>36.34</v>
       </c>
       <c r="P45" t="n">
-        <v>300.14</v>
+        <v>1994.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>414.5</v>
+        <v>4180.19</v>
       </c>
       <c r="R45" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="S45" t="n">
-        <v>43.95</v>
+        <v>33.8</v>
       </c>
       <c r="T45" t="n">
-        <v>44.67</v>
+        <v>34.24</v>
       </c>
       <c r="U45" t="n">
-        <v>43.8</v>
+        <v>33.49</v>
       </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
@@ -3747,69 +3747,69 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>601689</v>
+        <v>300450</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>56.27</v>
+        <v>47.55</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.39</v>
+        <v>2.59</v>
       </c>
       <c r="E46" t="n">
-        <v>57.61</v>
+        <v>47.44</v>
       </c>
       <c r="F46" t="n">
-        <v>57.63</v>
+        <v>47.99</v>
       </c>
       <c r="G46" t="n">
-        <v>59.71</v>
+        <v>49.12</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.667</v>
+        <v>-1.53</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.9</v>
+        <v>-1.571</v>
       </c>
       <c r="J46" t="n">
-        <v>34.77</v>
+        <v>33.68</v>
       </c>
       <c r="K46" t="n">
-        <v>38.79</v>
+        <v>38.38</v>
       </c>
       <c r="L46" t="n">
-        <v>26.73</v>
+        <v>24.28</v>
       </c>
       <c r="M46" t="n">
-        <v>27.99</v>
+        <v>44.25</v>
       </c>
       <c r="N46" t="n">
-        <v>28.67</v>
+        <v>41.07</v>
       </c>
       <c r="O46" t="n">
-        <v>32.82</v>
+        <v>42.22</v>
       </c>
       <c r="P46" t="n">
-        <v>2026.29</v>
+        <v>4145.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>2239.06</v>
+        <v>4558.54</v>
       </c>
       <c r="R46" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="S46" t="n">
-        <v>57.58</v>
+        <v>46.6</v>
       </c>
       <c r="T46" t="n">
-        <v>57.65</v>
+        <v>48.95</v>
       </c>
       <c r="U46" t="n">
-        <v>55.95</v>
+        <v>46.6</v>
       </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
@@ -3820,69 +3820,69 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2050</v>
+        <v>603200</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>41.77</v>
+        <v>55.8</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.31</v>
+        <v>-0.73</v>
       </c>
       <c r="E47" t="n">
-        <v>42.52</v>
+        <v>57.12</v>
       </c>
       <c r="F47" t="n">
-        <v>42.89</v>
+        <v>57.63</v>
       </c>
       <c r="G47" t="n">
-        <v>44.64</v>
+        <v>61.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.906</v>
+        <v>-4.708</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.879</v>
+        <v>-4.795</v>
       </c>
       <c r="J47" t="n">
-        <v>26.17</v>
+        <v>22.02</v>
       </c>
       <c r="K47" t="n">
-        <v>31.97</v>
+        <v>26.79</v>
       </c>
       <c r="L47" t="n">
-        <v>14.55</v>
+        <v>12.47</v>
       </c>
       <c r="M47" t="n">
-        <v>27.91</v>
+        <v>25.81</v>
       </c>
       <c r="N47" t="n">
-        <v>30.77</v>
+        <v>24.72</v>
       </c>
       <c r="O47" t="n">
-        <v>36.2</v>
+        <v>30.07</v>
       </c>
       <c r="P47" t="n">
-        <v>3992.93</v>
+        <v>374.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>7035.29</v>
+        <v>502.89</v>
       </c>
       <c r="R47" t="n">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="S47" t="n">
-        <v>41.9</v>
+        <v>56.9</v>
       </c>
       <c r="T47" t="n">
-        <v>42.25</v>
+        <v>57.67</v>
       </c>
       <c r="U47" t="n">
-        <v>41.4</v>
+        <v>55.66</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
@@ -3893,69 +3893,69 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>887</v>
+        <v>300409</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>道氏技术</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17.46</v>
+        <v>24.22</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.74</v>
+        <v>0.83</v>
       </c>
       <c r="E48" t="n">
-        <v>17.85</v>
+        <v>24.49</v>
       </c>
       <c r="F48" t="n">
-        <v>17.95</v>
+        <v>24.69</v>
       </c>
       <c r="G48" t="n">
-        <v>18.51</v>
+        <v>26.3</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.741</v>
+        <v>-1.129</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.758</v>
+        <v>-1.003</v>
       </c>
       <c r="J48" t="n">
-        <v>30.57</v>
+        <v>22.34</v>
       </c>
       <c r="K48" t="n">
-        <v>36.96</v>
+        <v>24.85</v>
       </c>
       <c r="L48" t="n">
-        <v>17.8</v>
+        <v>17.34</v>
       </c>
       <c r="M48" t="n">
-        <v>27.96</v>
+        <v>33.9</v>
       </c>
       <c r="N48" t="n">
-        <v>29.96</v>
+        <v>35.24</v>
       </c>
       <c r="O48" t="n">
-        <v>32.6</v>
+        <v>40.94</v>
       </c>
       <c r="P48" t="n">
-        <v>920.77</v>
+        <v>1420.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>1638.27</v>
+        <v>3494.6</v>
       </c>
       <c r="R48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="S48" t="n">
-        <v>17.6</v>
+        <v>24.09</v>
       </c>
       <c r="T48" t="n">
-        <v>17.72</v>
+        <v>24.66</v>
       </c>
       <c r="U48" t="n">
-        <v>17.36</v>
+        <v>24.02</v>
       </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
@@ -3966,69 +3966,69 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>603236</v>
+        <v>2202</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>72.58</v>
+        <v>22.89</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.24</v>
+        <v>-5.49</v>
       </c>
       <c r="E49" t="n">
-        <v>73.47</v>
+        <v>24.57</v>
       </c>
       <c r="F49" t="n">
-        <v>73.39</v>
+        <v>26.2</v>
       </c>
       <c r="G49" t="n">
-        <v>75.90000000000001</v>
+        <v>28.02</v>
       </c>
       <c r="H49" t="n">
-        <v>-3.039</v>
+        <v>-0.923</v>
       </c>
       <c r="I49" t="n">
-        <v>-3.286</v>
+        <v>-0.193</v>
       </c>
       <c r="J49" t="n">
-        <v>35.52</v>
+        <v>8.93</v>
       </c>
       <c r="K49" t="n">
-        <v>32.51</v>
+        <v>11.74</v>
       </c>
       <c r="L49" t="n">
-        <v>41.53</v>
+        <v>3.3</v>
       </c>
       <c r="M49" t="n">
-        <v>37.69</v>
+        <v>16.58</v>
       </c>
       <c r="N49" t="n">
-        <v>34.84</v>
+        <v>29.71</v>
       </c>
       <c r="O49" t="n">
-        <v>35.08</v>
+        <v>41.11</v>
       </c>
       <c r="P49" t="n">
-        <v>423.46</v>
+        <v>22857.68</v>
       </c>
       <c r="Q49" t="n">
-        <v>486.77</v>
+        <v>28391.1</v>
       </c>
       <c r="R49" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S49" t="n">
-        <v>73.5</v>
+        <v>23.84</v>
       </c>
       <c r="T49" t="n">
-        <v>74.55</v>
+        <v>23.84</v>
       </c>
       <c r="U49" t="n">
-        <v>71.90000000000001</v>
+        <v>22.8</v>
       </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
@@ -4039,69 +4039,69 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>603072</v>
+        <v>600990</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>天和磁材</t>
+          <t>四创电子</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>35.92</v>
+        <v>21.75</v>
       </c>
       <c r="D50" t="n">
-        <v>2.22</v>
+        <v>0.46</v>
       </c>
       <c r="E50" t="n">
-        <v>35.77</v>
+        <v>22.23</v>
       </c>
       <c r="F50" t="n">
-        <v>35.79</v>
+        <v>22.44</v>
       </c>
       <c r="G50" t="n">
-        <v>37.4</v>
+        <v>23.56</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.616</v>
+        <v>-1.243</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.656</v>
+        <v>-1.223</v>
       </c>
       <c r="J50" t="n">
-        <v>52.21</v>
+        <v>17.43</v>
       </c>
       <c r="K50" t="n">
-        <v>43.87</v>
+        <v>22.12</v>
       </c>
       <c r="L50" t="n">
-        <v>68.89</v>
+        <v>8.07</v>
       </c>
       <c r="M50" t="n">
-        <v>45</v>
+        <v>27.13</v>
       </c>
       <c r="N50" t="n">
-        <v>38.75</v>
+        <v>29.13</v>
       </c>
       <c r="O50" t="n">
-        <v>39.21</v>
+        <v>34.03</v>
       </c>
       <c r="P50" t="n">
-        <v>151.45</v>
+        <v>225.42</v>
       </c>
       <c r="Q50" t="n">
-        <v>220.59</v>
+        <v>400.7</v>
       </c>
       <c r="R50" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S50" t="n">
-        <v>35.44</v>
+        <v>21.5</v>
       </c>
       <c r="T50" t="n">
-        <v>36.09</v>
+        <v>21.98</v>
       </c>
       <c r="U50" t="n">
-        <v>35.14</v>
+        <v>21.5</v>
       </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
@@ -4112,69 +4112,69 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>301023</v>
+        <v>2025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>奕帆传动</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38.38</v>
+        <v>66.72</v>
       </c>
       <c r="D51" t="n">
-        <v>3.45</v>
+        <v>10.01</v>
       </c>
       <c r="E51" t="n">
-        <v>38.23</v>
+        <v>63.25</v>
       </c>
       <c r="F51" t="n">
-        <v>38.66</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>40.52</v>
+        <v>61.43</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.781</v>
+        <v>2.558</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.701</v>
+        <v>2.634</v>
       </c>
       <c r="J51" t="n">
-        <v>25.39</v>
+        <v>54.39</v>
       </c>
       <c r="K51" t="n">
-        <v>22.54</v>
+        <v>54.02</v>
       </c>
       <c r="L51" t="n">
-        <v>31.09</v>
+        <v>55.13</v>
       </c>
       <c r="M51" t="n">
-        <v>43.37</v>
+        <v>62.13</v>
       </c>
       <c r="N51" t="n">
-        <v>39.09</v>
+        <v>60.21</v>
       </c>
       <c r="O51" t="n">
-        <v>41.66</v>
+        <v>58.91</v>
       </c>
       <c r="P51" t="n">
-        <v>175.72</v>
+        <v>3329.69</v>
       </c>
       <c r="Q51" t="n">
-        <v>127.16</v>
+        <v>3710.76</v>
       </c>
       <c r="R51" t="n">
-        <v>1.38</v>
+        <v>0.9</v>
       </c>
       <c r="S51" t="n">
-        <v>37.09</v>
+        <v>62.93</v>
       </c>
       <c r="T51" t="n">
-        <v>38.9</v>
+        <v>66.72</v>
       </c>
       <c r="U51" t="n">
-        <v>37.06</v>
+        <v>62.6</v>
       </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
@@ -4185,69 +4185,69 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2074</v>
+        <v>600584</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>33.8</v>
+        <v>38.82</v>
       </c>
       <c r="D52" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="E52" t="n">
-        <v>34.74</v>
+        <v>38.77</v>
       </c>
       <c r="F52" t="n">
-        <v>35.95</v>
+        <v>39.27</v>
       </c>
       <c r="G52" t="n">
-        <v>36.98</v>
+        <v>41.87</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.886</v>
+        <v>-1.928</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.504</v>
+        <v>-1.661</v>
       </c>
       <c r="J52" t="n">
-        <v>13.28</v>
+        <v>15.37</v>
       </c>
       <c r="K52" t="n">
-        <v>24.06</v>
+        <v>13.94</v>
       </c>
       <c r="L52" t="n">
-        <v>-8.27</v>
+        <v>18.22</v>
       </c>
       <c r="M52" t="n">
-        <v>22.89</v>
+        <v>37.33</v>
       </c>
       <c r="N52" t="n">
-        <v>29.83</v>
+        <v>36.65</v>
       </c>
       <c r="O52" t="n">
-        <v>36.34</v>
+        <v>41.43</v>
       </c>
       <c r="P52" t="n">
-        <v>1994.7</v>
+        <v>2738.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>4180.19</v>
+        <v>5360.89</v>
       </c>
       <c r="R52" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="S52" t="n">
-        <v>33.8</v>
+        <v>38.7</v>
       </c>
       <c r="T52" t="n">
-        <v>34.24</v>
+        <v>39.06</v>
       </c>
       <c r="U52" t="n">
-        <v>33.49</v>
+        <v>38.54</v>
       </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
@@ -4258,69 +4258,69 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>300450</v>
+        <v>300759</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>47.55</v>
+        <v>30.1</v>
       </c>
       <c r="D53" t="n">
-        <v>2.59</v>
+        <v>0.1</v>
       </c>
       <c r="E53" t="n">
-        <v>47.44</v>
+        <v>29.83</v>
       </c>
       <c r="F53" t="n">
-        <v>47.99</v>
+        <v>27.99</v>
       </c>
       <c r="G53" t="n">
-        <v>49.12</v>
+        <v>27.6</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.53</v>
+        <v>0.292</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.571</v>
+        <v>-0.275</v>
       </c>
       <c r="J53" t="n">
-        <v>33.68</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>38.38</v>
+        <v>69</v>
       </c>
       <c r="L53" t="n">
-        <v>24.28</v>
+        <v>99.78</v>
       </c>
       <c r="M53" t="n">
-        <v>44.25</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>41.07</v>
+        <v>63.79</v>
       </c>
       <c r="O53" t="n">
-        <v>42.22</v>
+        <v>56.3</v>
       </c>
       <c r="P53" t="n">
-        <v>4145.92</v>
+        <v>4449.52</v>
       </c>
       <c r="Q53" t="n">
-        <v>4558.54</v>
+        <v>3144.88</v>
       </c>
       <c r="R53" t="n">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="S53" t="n">
-        <v>46.6</v>
+        <v>30.2</v>
       </c>
       <c r="T53" t="n">
-        <v>48.95</v>
+        <v>31.3</v>
       </c>
       <c r="U53" t="n">
-        <v>46.6</v>
+        <v>29.35</v>
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
@@ -4331,69 +4331,69 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>688778</v>
+        <v>301333</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>诺思格</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>69.83</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>70.89</v>
+        <v>68.31</v>
       </c>
       <c r="F54" t="n">
-        <v>72.05</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>73.44</v>
+        <v>63.31</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.51</v>
+        <v>-0.316</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.497</v>
+        <v>-1.446</v>
       </c>
       <c r="J54" t="n">
-        <v>35.1</v>
+        <v>65.83</v>
       </c>
       <c r="K54" t="n">
-        <v>46.1</v>
+        <v>66.06</v>
       </c>
       <c r="L54" t="n">
-        <v>13.1</v>
+        <v>65.37</v>
       </c>
       <c r="M54" t="n">
-        <v>36.1</v>
+        <v>53.14</v>
       </c>
       <c r="N54" t="n">
-        <v>37.83</v>
+        <v>51.45</v>
       </c>
       <c r="O54" t="n">
-        <v>40.65</v>
+        <v>49.85</v>
       </c>
       <c r="P54" t="n">
-        <v>291.97</v>
+        <v>242.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>509.42</v>
+        <v>232.44</v>
       </c>
       <c r="R54" t="n">
-        <v>0.57</v>
+        <v>1.04</v>
       </c>
       <c r="S54" t="n">
-        <v>69.8</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="T54" t="n">
-        <v>71.45</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="U54" t="n">
-        <v>69.31</v>
+        <v>63.77</v>
       </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
@@ -4404,69 +4404,69 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>688116</v>
+        <v>963</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>天奈科技</t>
+          <t>华东医药</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38.03</v>
+        <v>35.94</v>
       </c>
       <c r="D55" t="n">
-        <v>3.06</v>
+        <v>-0.96</v>
       </c>
       <c r="E55" t="n">
-        <v>38.46</v>
+        <v>36.15</v>
       </c>
       <c r="F55" t="n">
-        <v>39.59</v>
+        <v>35.34</v>
       </c>
       <c r="G55" t="n">
-        <v>41.11</v>
+        <v>35.29</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.77</v>
+        <v>0.065</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.549</v>
+        <v>-0.199</v>
       </c>
       <c r="J55" t="n">
-        <v>20.17</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>24.47</v>
+        <v>70.27</v>
       </c>
       <c r="L55" t="n">
-        <v>11.57</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>32.66</v>
+        <v>55.01</v>
       </c>
       <c r="N55" t="n">
-        <v>32</v>
+        <v>53.52</v>
       </c>
       <c r="O55" t="n">
-        <v>35.06</v>
+        <v>49.16</v>
       </c>
       <c r="P55" t="n">
-        <v>574.46</v>
+        <v>888.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>759.78</v>
+        <v>1072.42</v>
       </c>
       <c r="R55" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="S55" t="n">
-        <v>36.99</v>
+        <v>36.38</v>
       </c>
       <c r="T55" t="n">
-        <v>38.28</v>
+        <v>36.48</v>
       </c>
       <c r="U55" t="n">
-        <v>36.99</v>
+        <v>35.63</v>
       </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
@@ -4477,69 +4477,69 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>603200</v>
+        <v>603658</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>安图生物</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55.8</v>
+        <v>34.6</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.73</v>
+        <v>1.82</v>
       </c>
       <c r="E56" t="n">
-        <v>57.12</v>
+        <v>34.17</v>
       </c>
       <c r="F56" t="n">
-        <v>57.63</v>
+        <v>33.69</v>
       </c>
       <c r="G56" t="n">
-        <v>61.7</v>
+        <v>34.16</v>
       </c>
       <c r="H56" t="n">
-        <v>-4.708</v>
+        <v>-0.393</v>
       </c>
       <c r="I56" t="n">
-        <v>-4.795</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>22.02</v>
+        <v>74.62</v>
       </c>
       <c r="K56" t="n">
-        <v>26.79</v>
+        <v>58.07</v>
       </c>
       <c r="L56" t="n">
-        <v>12.47</v>
+        <v>107.73</v>
       </c>
       <c r="M56" t="n">
-        <v>25.81</v>
+        <v>62.74</v>
       </c>
       <c r="N56" t="n">
-        <v>24.72</v>
+        <v>52.92</v>
       </c>
       <c r="O56" t="n">
-        <v>30.07</v>
+        <v>47.57</v>
       </c>
       <c r="P56" t="n">
-        <v>374.04</v>
+        <v>183.36</v>
       </c>
       <c r="Q56" t="n">
-        <v>502.89</v>
+        <v>192.9</v>
       </c>
       <c r="R56" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="S56" t="n">
-        <v>56.9</v>
+        <v>33.93</v>
       </c>
       <c r="T56" t="n">
-        <v>57.67</v>
+        <v>34.69</v>
       </c>
       <c r="U56" t="n">
-        <v>55.66</v>
+        <v>33.66</v>
       </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
@@ -4550,1021 +4550,72 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>300409</v>
+        <v>300357</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>道氏技术</t>
+          <t>我武生物</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>24.22</v>
+        <v>25.65</v>
       </c>
       <c r="D57" t="n">
-        <v>0.83</v>
+        <v>0.47</v>
       </c>
       <c r="E57" t="n">
-        <v>24.49</v>
+        <v>25.94</v>
       </c>
       <c r="F57" t="n">
-        <v>24.69</v>
+        <v>25.26</v>
       </c>
       <c r="G57" t="n">
-        <v>26.3</v>
+        <v>25.13</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.129</v>
+        <v>-0.154</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.003</v>
+        <v>-0.419</v>
       </c>
       <c r="J57" t="n">
-        <v>22.34</v>
+        <v>71.95</v>
       </c>
       <c r="K57" t="n">
-        <v>24.85</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>17.34</v>
+        <v>78.86</v>
       </c>
       <c r="M57" t="n">
-        <v>33.9</v>
+        <v>53.39</v>
       </c>
       <c r="N57" t="n">
-        <v>35.24</v>
+        <v>51.08</v>
       </c>
       <c r="O57" t="n">
-        <v>40.94</v>
+        <v>46.52</v>
       </c>
       <c r="P57" t="n">
-        <v>1420.5</v>
+        <v>829.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>3494.6</v>
+        <v>1140.24</v>
       </c>
       <c r="R57" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="S57" t="n">
-        <v>24.09</v>
+        <v>25.68</v>
       </c>
       <c r="T57" t="n">
-        <v>24.66</v>
+        <v>26.03</v>
       </c>
       <c r="U57" t="n">
-        <v>24.02</v>
+        <v>25.22</v>
       </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2202</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>金风科技</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-5.49</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="F58" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G58" t="n">
-        <v>28.02</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0.923</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-0.193</v>
-      </c>
-      <c r="J58" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="K58" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M58" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="N58" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="O58" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="P58" t="n">
-        <v>22857.68</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>28391.1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="S58" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="T58" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="U58" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>688066</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>航天宏图</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="E59" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F59" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="G59" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-2.221</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="J59" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="K59" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="M59" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="N59" t="n">
-        <v>22.52</v>
-      </c>
-      <c r="O59" t="n">
-        <v>33.12</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1060.07</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1008.34</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S59" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="T59" t="n">
-        <v>17</v>
-      </c>
-      <c r="U59" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>600990</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>四创电子</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E60" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="G60" t="n">
-        <v>23.56</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-1.243</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-1.223</v>
-      </c>
-      <c r="J60" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="K60" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="L60" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="M60" t="n">
-        <v>27.13</v>
-      </c>
-      <c r="N60" t="n">
-        <v>29.13</v>
-      </c>
-      <c r="O60" t="n">
-        <v>34.03</v>
-      </c>
-      <c r="P60" t="n">
-        <v>225.42</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>400.7</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S60" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="T60" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="U60" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>航天电器</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>66.72</v>
-      </c>
-      <c r="D61" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="E61" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="F61" t="n">
-        <v>64.06999999999999</v>
-      </c>
-      <c r="G61" t="n">
-        <v>61.43</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2.558</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.634</v>
-      </c>
-      <c r="J61" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="K61" t="n">
-        <v>54.02</v>
-      </c>
-      <c r="L61" t="n">
-        <v>55.13</v>
-      </c>
-      <c r="M61" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="N61" t="n">
-        <v>60.21</v>
-      </c>
-      <c r="O61" t="n">
-        <v>58.91</v>
-      </c>
-      <c r="P61" t="n">
-        <v>3329.69</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>3710.76</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S61" t="n">
-        <v>62.93</v>
-      </c>
-      <c r="T61" t="n">
-        <v>66.72</v>
-      </c>
-      <c r="U61" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>600584</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>38.82</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E62" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="F62" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="G62" t="n">
-        <v>41.87</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-1.928</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-1.661</v>
-      </c>
-      <c r="J62" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="K62" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="L62" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="M62" t="n">
-        <v>37.33</v>
-      </c>
-      <c r="N62" t="n">
-        <v>36.65</v>
-      </c>
-      <c r="O62" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="P62" t="n">
-        <v>2738.21</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>5360.89</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="S62" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="T62" t="n">
-        <v>39.06</v>
-      </c>
-      <c r="U62" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>688295</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>中复神鹰</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="E63" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="F63" t="n">
-        <v>56.07</v>
-      </c>
-      <c r="G63" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="H63" t="n">
-        <v>3.982</v>
-      </c>
-      <c r="I63" t="n">
-        <v>5.557</v>
-      </c>
-      <c r="J63" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="K63" t="n">
-        <v>27.17</v>
-      </c>
-      <c r="L63" t="n">
-        <v>-17.32</v>
-      </c>
-      <c r="M63" t="n">
-        <v>32</v>
-      </c>
-      <c r="N63" t="n">
-        <v>48.66</v>
-      </c>
-      <c r="O63" t="n">
-        <v>56.07</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1553.26</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2868.21</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="S63" t="n">
-        <v>50.01</v>
-      </c>
-      <c r="T63" t="n">
-        <v>50.59</v>
-      </c>
-      <c r="U63" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>300759</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>康龙化成</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E64" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="F64" t="n">
-        <v>27.99</v>
-      </c>
-      <c r="G64" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="I64" t="n">
-        <v>-0.275</v>
-      </c>
-      <c r="J64" t="n">
-        <v>79.26000000000001</v>
-      </c>
-      <c r="K64" t="n">
-        <v>69</v>
-      </c>
-      <c r="L64" t="n">
-        <v>99.78</v>
-      </c>
-      <c r="M64" t="n">
-        <v>72.84999999999999</v>
-      </c>
-      <c r="N64" t="n">
-        <v>63.79</v>
-      </c>
-      <c r="O64" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="P64" t="n">
-        <v>4449.52</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3144.88</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S64" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="T64" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="U64" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>688621</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>阳光诺和</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E65" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F65" t="n">
-        <v>64.56999999999999</v>
-      </c>
-      <c r="G65" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-0.286</v>
-      </c>
-      <c r="J65" t="n">
-        <v>72.89</v>
-      </c>
-      <c r="K65" t="n">
-        <v>72.39</v>
-      </c>
-      <c r="L65" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="M65" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="N65" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="O65" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="P65" t="n">
-        <v>258.82</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>224.32</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S65" t="n">
-        <v>66.65000000000001</v>
-      </c>
-      <c r="T65" t="n">
-        <v>68.03</v>
-      </c>
-      <c r="U65" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>301333</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>诺思格</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
-        <v>68.31</v>
-      </c>
-      <c r="F66" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="G66" t="n">
-        <v>63.31</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-0.316</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-1.446</v>
-      </c>
-      <c r="J66" t="n">
-        <v>65.83</v>
-      </c>
-      <c r="K66" t="n">
-        <v>66.06</v>
-      </c>
-      <c r="L66" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="M66" t="n">
-        <v>53.14</v>
-      </c>
-      <c r="N66" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="O66" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="P66" t="n">
-        <v>242.45</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>232.44</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="S66" t="n">
-        <v>66.31999999999999</v>
-      </c>
-      <c r="T66" t="n">
-        <v>67.79000000000001</v>
-      </c>
-      <c r="U66" t="n">
-        <v>63.77</v>
-      </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>963</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>华东医药</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>35.94</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="E67" t="n">
-        <v>36.15</v>
-      </c>
-      <c r="F67" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="G67" t="n">
-        <v>35.29</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.199</v>
-      </c>
-      <c r="J67" t="n">
-        <v>75.34999999999999</v>
-      </c>
-      <c r="K67" t="n">
-        <v>70.27</v>
-      </c>
-      <c r="L67" t="n">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="M67" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="N67" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="O67" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="P67" t="n">
-        <v>888.12</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1072.42</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="S67" t="n">
-        <v>36.38</v>
-      </c>
-      <c r="T67" t="n">
-        <v>36.48</v>
-      </c>
-      <c r="U67" t="n">
-        <v>35.63</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>603658</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>安图生物</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E68" t="n">
-        <v>34.17</v>
-      </c>
-      <c r="F68" t="n">
-        <v>33.69</v>
-      </c>
-      <c r="G68" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-0.393</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-0.5610000000000001</v>
-      </c>
-      <c r="J68" t="n">
-        <v>74.62</v>
-      </c>
-      <c r="K68" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="L68" t="n">
-        <v>107.73</v>
-      </c>
-      <c r="M68" t="n">
-        <v>62.74</v>
-      </c>
-      <c r="N68" t="n">
-        <v>52.92</v>
-      </c>
-      <c r="O68" t="n">
-        <v>47.57</v>
-      </c>
-      <c r="P68" t="n">
-        <v>183.36</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>192.9</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="S68" t="n">
-        <v>33.93</v>
-      </c>
-      <c r="T68" t="n">
-        <v>34.69</v>
-      </c>
-      <c r="U68" t="n">
-        <v>33.66</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>300357</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>我武生物</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E69" t="n">
-        <v>25.94</v>
-      </c>
-      <c r="F69" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25.13</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-0.154</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-0.419</v>
-      </c>
-      <c r="J69" t="n">
-        <v>71.95</v>
-      </c>
-      <c r="K69" t="n">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="L69" t="n">
-        <v>78.86</v>
-      </c>
-      <c r="M69" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="N69" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="O69" t="n">
-        <v>46.52</v>
-      </c>
-      <c r="P69" t="n">
-        <v>829.85</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1140.24</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="S69" t="n">
-        <v>25.68</v>
-      </c>
-      <c r="T69" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="U69" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>688050</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>爱博医疗</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E70" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="F70" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="G70" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-1.803</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-1.985</v>
-      </c>
-      <c r="J70" t="n">
-        <v>51.59</v>
-      </c>
-      <c r="K70" t="n">
-        <v>47.12</v>
-      </c>
-      <c r="L70" t="n">
-        <v>60.54</v>
-      </c>
-      <c r="M70" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="N70" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="O70" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="P70" t="n">
-        <v>81.13</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>169.04</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="S70" t="n">
-        <v>51.01</v>
-      </c>
-      <c r="T70" t="n">
-        <v>51.59</v>
-      </c>
-      <c r="U70" t="n">
-        <v>50.73</v>
-      </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
